--- a/Result/profitability/8299.xlsx
+++ b/Result/profitability/8299.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.01</v>
       </c>
       <c r="M2" t="n">
-        <v>16.00125</v>
+        <v>30.40125</v>
       </c>
       <c r="N2" t="n">
-        <v>33.1325</v>
+        <v>37.64125000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.05</v>
       </c>
       <c r="M3" t="n">
-        <v>15.71125</v>
+        <v>29.06875</v>
       </c>
       <c r="N3" t="n">
-        <v>30.71125</v>
+        <v>35.08875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>14.31875</v>
+        <v>28.44875</v>
       </c>
       <c r="N4" t="n">
-        <v>27.3</v>
+        <v>31.5725</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>13.8025</v>
+        <v>28.17375</v>
       </c>
       <c r="N5" t="n">
-        <v>24.12625</v>
+        <v>28.645</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>3.56</v>
       </c>
       <c r="M6" t="n">
-        <v>13.7975</v>
+        <v>27.275</v>
       </c>
       <c r="N6" t="n">
-        <v>23.1475</v>
+        <v>27.24</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>12.84125</v>
+        <v>24.8825</v>
       </c>
       <c r="N7" t="n">
-        <v>21.0325</v>
+        <v>23.96625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>10.455</v>
+        <v>16.67625</v>
       </c>
       <c r="N8" t="n">
-        <v>17.46375</v>
+        <v>17.905</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>67888</v>
+      </c>
+      <c r="D75" t="n">
+        <v>23523</v>
+      </c>
+      <c r="E75" t="n">
+        <v>44365</v>
+      </c>
+      <c r="F75" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>26370</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>38.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4704</v>
+      </c>
+      <c r="J75" t="n">
+        <v>31075</v>
+      </c>
+      <c r="K75" t="n">
+        <v>26217</v>
+      </c>
+      <c r="L75" t="n">
+        <v>118.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>30.57125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>40.205</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7234011627906975</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.529999999999994</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05710126172759611</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>114.97</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>31.93611111111111</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>36.14999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.238013698630137</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
